--- a/ED_Fig2n.xlsx
+++ b/ED_Fig2n.xlsx
@@ -400,10 +400,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>1.099433479455197</v>
+        <v>1.099785623093096</v>
       </c>
       <c r="C2">
-        <v>0.04957452428840745</v>
+        <v>0.04997142684295464</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -411,10 +411,10 @@
         <v>71</v>
       </c>
       <c r="B3">
-        <v>1.560352664392499</v>
+        <v>1.560733889203865</v>
       </c>
       <c r="C3">
-        <v>0.02884985399895988</v>
+        <v>0.02899716230967756</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -422,10 +422,10 @@
         <v>72</v>
       </c>
       <c r="B4">
-        <v>1.569910833227701</v>
+        <v>1.570266686242576</v>
       </c>
       <c r="C4">
-        <v>0.04460133192148352</v>
+        <v>0.04454887801178831</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -433,10 +433,10 @@
         <v>77</v>
       </c>
       <c r="B5">
-        <v>1.284261507588227</v>
+        <v>1.284646878988338</v>
       </c>
       <c r="C5">
-        <v>0.04509455132865097</v>
+        <v>0.04462008191376825</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -444,10 +444,10 @@
         <v>85</v>
       </c>
       <c r="B6">
-        <v>1.535172830971694</v>
+        <v>1.535683927211244</v>
       </c>
       <c r="C6">
-        <v>0.02959434838347808</v>
+        <v>0.02901601026848526</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -455,10 +455,10 @@
         <v>88</v>
       </c>
       <c r="B7">
-        <v>1.654901773326637</v>
+        <v>1.655529048884231</v>
       </c>
       <c r="C7">
-        <v>0.0132237114994828</v>
+        <v>0.01242445901365212</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -466,10 +466,10 @@
         <v>91</v>
       </c>
       <c r="B8">
-        <v>1.476680501372273</v>
+        <v>1.477545459150631</v>
       </c>
       <c r="C8">
-        <v>0.05023510793229831</v>
+        <v>0.04876374061030887</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -477,10 +477,10 @@
         <v>102</v>
       </c>
       <c r="B9">
-        <v>1.56908730269527</v>
+        <v>1.56945983818803</v>
       </c>
       <c r="C9">
-        <v>0.006457219702832857</v>
+        <v>0.006324961214465403</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -488,10 +488,10 @@
         <v>108</v>
       </c>
       <c r="B10">
-        <v>1.633090293076688</v>
+        <v>1.63355336036133</v>
       </c>
       <c r="C10">
-        <v>0.04079874817443474</v>
+        <v>0.0400191210818909</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -499,10 +499,10 @@
         <v>110</v>
       </c>
       <c r="B11">
-        <v>1.5396369720153</v>
+        <v>1.539938709553155</v>
       </c>
       <c r="C11">
-        <v>0.02860281980974704</v>
+        <v>0.02824848523392967</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -510,10 +510,10 @@
         <v>115</v>
       </c>
       <c r="B12">
-        <v>1.743217092893423</v>
+        <v>1.74372789034045</v>
       </c>
       <c r="C12">
-        <v>0.008338874068012</v>
+        <v>0.007836105456449548</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -521,10 +521,10 @@
         <v>116</v>
       </c>
       <c r="B13">
-        <v>1.793876361303762</v>
+        <v>1.794159061475177</v>
       </c>
       <c r="C13">
-        <v>0.01871647037658653</v>
+        <v>0.01867997753590541</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -532,10 +532,10 @@
         <v>120</v>
       </c>
       <c r="B14">
-        <v>1.75654046616903</v>
+        <v>1.756950398310273</v>
       </c>
       <c r="C14">
-        <v>0.02491622413959576</v>
+        <v>0.02421466810310896</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -543,10 +543,10 @@
         <v>124</v>
       </c>
       <c r="B15">
-        <v>1.555183182011292</v>
+        <v>1.555370472896029</v>
       </c>
       <c r="C15">
-        <v>0.04676030670854589</v>
+        <v>0.04691014869080832</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -554,10 +554,10 @@
         <v>130</v>
       </c>
       <c r="B16">
-        <v>1.153404267531167</v>
+        <v>1.153627021972459</v>
       </c>
       <c r="C16">
-        <v>0.01823176162568293</v>
+        <v>0.01837688256661239</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -565,10 +565,10 @@
         <v>135</v>
       </c>
       <c r="B17">
-        <v>1.297955899829304</v>
+        <v>1.298728849454393</v>
       </c>
       <c r="C17">
-        <v>0.01092353704612993</v>
+        <v>0.01094057970027194</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -576,10 +576,10 @@
         <v>143</v>
       </c>
       <c r="B18">
-        <v>1.543896936266179</v>
+        <v>1.544505959981581</v>
       </c>
       <c r="C18">
-        <v>0.02538496567128489</v>
+        <v>0.02433029712010856</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -587,10 +587,10 @@
         <v>146</v>
       </c>
       <c r="B19">
-        <v>1.524517760636149</v>
+        <v>1.524977776309856</v>
       </c>
       <c r="C19">
-        <v>0.03428770937431686</v>
+        <v>0.03463414005069348</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -598,10 +598,10 @@
         <v>184</v>
       </c>
       <c r="B20">
-        <v>1.429422566545144</v>
+        <v>1.430072081772516</v>
       </c>
       <c r="C20">
-        <v>0.01785943258918651</v>
+        <v>0.01888178236118298</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -609,10 +609,10 @@
         <v>185</v>
       </c>
       <c r="B21">
-        <v>1.431062898534432</v>
+        <v>1.431702436990758</v>
       </c>
       <c r="C21">
-        <v>0.01980057445020018</v>
+        <v>0.02022726844699303</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -620,10 +620,10 @@
         <v>315</v>
       </c>
       <c r="B22">
-        <v>0.7581002462956339</v>
+        <v>0.7583973708447166</v>
       </c>
       <c r="C22">
-        <v>0.02393664160932083</v>
+        <v>0.02351344334227741</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -631,10 +631,10 @@
         <v>361</v>
       </c>
       <c r="B23">
-        <v>1.245274131135377</v>
+        <v>1.245787554664431</v>
       </c>
       <c r="C23">
-        <v>0.002180456723584206</v>
+        <v>0.002319453479737566</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -642,10 +642,10 @@
         <v>362</v>
       </c>
       <c r="B24">
-        <v>1.269686806085464</v>
+        <v>1.270120340706564</v>
       </c>
       <c r="C24">
-        <v>0.02691428581974173</v>
+        <v>0.02736901567541156</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -653,10 +653,10 @@
         <v>368</v>
       </c>
       <c r="B25">
-        <v>1.13711305380806</v>
+        <v>1.137725227241843</v>
       </c>
       <c r="C25">
-        <v>0.03643871116590228</v>
+        <v>0.03735520823386088</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -664,10 +664,10 @@
         <v>375</v>
       </c>
       <c r="B26">
-        <v>1.04709370171158</v>
+        <v>1.047390190658503</v>
       </c>
       <c r="C26">
-        <v>0.03210292090797729</v>
+        <v>0.03220090873404909</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -675,10 +675,10 @@
         <v>381</v>
       </c>
       <c r="B27">
-        <v>1.123323408888614</v>
+        <v>1.123577781858643</v>
       </c>
       <c r="C27">
-        <v>0.03196530364400115</v>
+        <v>0.03189843417454143</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -686,10 +686,10 @@
         <v>386</v>
       </c>
       <c r="B28">
-        <v>1.233344878241409</v>
+        <v>1.233504629227515</v>
       </c>
       <c r="C28">
-        <v>0.04115913918221043</v>
+        <v>0.04089967992190621</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -697,10 +697,10 @@
         <v>391</v>
       </c>
       <c r="B29">
-        <v>1.251703276921228</v>
+        <v>1.252055177801223</v>
       </c>
       <c r="C29">
-        <v>0.07745630246591888</v>
+        <v>0.07720826642593043</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -708,10 +708,10 @@
         <v>396</v>
       </c>
       <c r="B30">
-        <v>1.213704525063581</v>
+        <v>1.214240278243575</v>
       </c>
       <c r="C30">
-        <v>0.04050843965352274</v>
+        <v>0.03996525811237567</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -719,10 +719,10 @@
         <v>398</v>
       </c>
       <c r="B31">
-        <v>1.186975495132599</v>
+        <v>1.187412092943069</v>
       </c>
       <c r="C31">
-        <v>0.02301864987775535</v>
+        <v>0.02226354900811788</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -730,10 +730,10 @@
         <v>418</v>
       </c>
       <c r="B32">
-        <v>1.499491137771092</v>
+        <v>1.499911281471415</v>
       </c>
       <c r="C32">
-        <v>0.01753678403421829</v>
+        <v>0.01781440074865569</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -741,10 +741,10 @@
         <v>419</v>
       </c>
       <c r="B33">
-        <v>1.548361261418965</v>
+        <v>1.548690747490026</v>
       </c>
       <c r="C33">
-        <v>0.03087270556003152</v>
+        <v>0.03137081516235309</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -752,10 +752,10 @@
         <v>423</v>
       </c>
       <c r="B34">
-        <v>1.537674531826034</v>
+        <v>1.538152212908774</v>
       </c>
       <c r="C34">
-        <v>0.009877817970217934</v>
+        <v>0.009190105417536568</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -763,10 +763,10 @@
         <v>424</v>
       </c>
       <c r="B35">
-        <v>1.479373741021006</v>
+        <v>1.480028683807741</v>
       </c>
       <c r="C35">
-        <v>0.0256419603220409</v>
+        <v>0.02459944213993702</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -774,10 +774,10 @@
         <v>428</v>
       </c>
       <c r="B36">
-        <v>1.255318549443109</v>
+        <v>1.255992195313371</v>
       </c>
       <c r="C36">
-        <v>0.01793643608061193</v>
+        <v>0.01902651360154106</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -785,10 +785,10 @@
         <v>447</v>
       </c>
       <c r="B37">
-        <v>1.468774245767452</v>
+        <v>1.469557208234019</v>
       </c>
       <c r="C37">
-        <v>0.0008965939013944818</v>
+        <v>0.002149966549432861</v>
       </c>
     </row>
   </sheetData>
@@ -814,10 +814,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>1.089642089689479</v>
+        <v>1.090280074657275</v>
       </c>
       <c r="C2">
-        <v>0.03439183367894177</v>
+        <v>0.03537197254204683</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -825,10 +825,10 @@
         <v>71</v>
       </c>
       <c r="B3">
-        <v>1.119690325580208</v>
+        <v>1.120353647894109</v>
       </c>
       <c r="C3">
-        <v>0.004315059031702411</v>
+        <v>0.005096181965007399</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -836,10 +836,10 @@
         <v>72</v>
       </c>
       <c r="B4">
-        <v>1.144531733415705</v>
+        <v>1.144969858731288</v>
       </c>
       <c r="C4">
-        <v>0.01169598082220806</v>
+        <v>0.01245086196470341</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -847,10 +847,10 @@
         <v>77</v>
       </c>
       <c r="B5">
-        <v>1.182912030660126</v>
+        <v>1.183370173327664</v>
       </c>
       <c r="C5">
-        <v>0.02192188993359123</v>
+        <v>0.02132266172018154</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -858,10 +858,10 @@
         <v>85</v>
       </c>
       <c r="B6">
-        <v>1.198608404967622</v>
+        <v>1.198769986853458</v>
       </c>
       <c r="C6">
-        <v>0.05295383523400776</v>
+        <v>0.05273712819777346</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -869,10 +869,10 @@
         <v>88</v>
       </c>
       <c r="B7">
-        <v>1.188442605479748</v>
+        <v>1.188864684506458</v>
       </c>
       <c r="C7">
-        <v>0.04815563496814546</v>
+        <v>0.04774251644499672</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -880,10 +880,10 @@
         <v>91</v>
       </c>
       <c r="B8">
-        <v>1.200390643868336</v>
+        <v>1.200741141518516</v>
       </c>
       <c r="C8">
-        <v>0.02783213332972193</v>
+        <v>0.02802284655317208</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -891,10 +891,10 @@
         <v>102</v>
       </c>
       <c r="B9">
-        <v>1.222052911260049</v>
+        <v>1.22256106409107</v>
       </c>
       <c r="C9">
-        <v>0.03724559760782502</v>
+        <v>0.03806507454588576</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -902,10 +902,10 @@
         <v>108</v>
       </c>
       <c r="B10">
-        <v>1.207940349292309</v>
+        <v>1.208273652681005</v>
       </c>
       <c r="C10">
-        <v>0.02785585048384584</v>
+        <v>0.0274487473713458</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -913,10 +913,10 @@
         <v>110</v>
       </c>
       <c r="B11">
-        <v>1.216052273117699</v>
+        <v>1.216407727724663</v>
       </c>
       <c r="C11">
-        <v>0.03126794626832369</v>
+        <v>0.03090416350534287</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -924,10 +924,10 @@
         <v>115</v>
       </c>
       <c r="B12">
-        <v>1.250177934246559</v>
+        <v>1.250259734138622</v>
       </c>
       <c r="C12">
-        <v>0.0519876374683983</v>
+        <v>0.05212638281173371</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -935,10 +935,10 @@
         <v>116</v>
       </c>
       <c r="B13">
-        <v>1.238104341736928</v>
+        <v>1.238322483286604</v>
       </c>
       <c r="C13">
-        <v>0.04827556497230426</v>
+        <v>0.04865000368723522</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -946,10 +946,10 @@
         <v>120</v>
       </c>
       <c r="B14">
-        <v>1.225918159478785</v>
+        <v>1.226322043354816</v>
       </c>
       <c r="C14">
-        <v>0.06194401429791629</v>
+        <v>0.06264142944747832</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -957,10 +957,10 @@
         <v>124</v>
       </c>
       <c r="B15">
-        <v>1.183455343853996</v>
+        <v>1.184129609497379</v>
       </c>
       <c r="C15">
-        <v>0.0384817028243899</v>
+        <v>0.03863863145022431</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -968,10 +968,10 @@
         <v>130</v>
       </c>
       <c r="B16">
-        <v>1.174741522641451</v>
+        <v>1.174989528703825</v>
       </c>
       <c r="C16">
-        <v>0.02176698676814658</v>
+        <v>0.02180853889361624</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -979,10 +979,10 @@
         <v>135</v>
       </c>
       <c r="B17">
-        <v>1.151964606456419</v>
+        <v>1.152303344287791</v>
       </c>
       <c r="C17">
-        <v>0.007270736736177732</v>
+        <v>0.007320656481465977</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -990,10 +990,10 @@
         <v>143</v>
       </c>
       <c r="B18">
-        <v>1.140660732011085</v>
+        <v>1.141056607392298</v>
       </c>
       <c r="C18">
-        <v>0.02959470881483421</v>
+        <v>0.02891498787860662</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1001,10 +1001,10 @@
         <v>146</v>
       </c>
       <c r="B19">
-        <v>1.140943888193634</v>
+        <v>1.141529949872639</v>
       </c>
       <c r="C19">
-        <v>0.003329014388327839</v>
+        <v>0.00417897910606039</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1012,10 +1012,10 @@
         <v>184</v>
       </c>
       <c r="B20">
-        <v>1.044498269844768</v>
+        <v>1.045267529861867</v>
       </c>
       <c r="C20">
-        <v>0.03646950412331997</v>
+        <v>0.03598008455612771</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1023,10 +1023,10 @@
         <v>185</v>
       </c>
       <c r="B21">
-        <v>1.024059361539596</v>
+        <v>1.024712583923088</v>
       </c>
       <c r="C21">
-        <v>0.02232003766350153</v>
+        <v>0.02183166038070521</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1034,10 +1034,10 @@
         <v>315</v>
       </c>
       <c r="B22">
-        <v>0.9281360163254558</v>
+        <v>0.9287161126547261</v>
       </c>
       <c r="C22">
-        <v>0.02780239214528361</v>
+        <v>0.02800881523600204</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1045,10 +1045,10 @@
         <v>361</v>
       </c>
       <c r="B23">
-        <v>1.057391074940592</v>
+        <v>1.057857470976088</v>
       </c>
       <c r="C23">
-        <v>0.006845364393966426</v>
+        <v>0.00605726434971773</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1056,10 +1056,10 @@
         <v>362</v>
       </c>
       <c r="B24">
-        <v>1.053438556395814</v>
+        <v>1.054086439718876</v>
       </c>
       <c r="C24">
-        <v>0.009018626194613612</v>
+        <v>0.008914699720979918</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1067,10 +1067,10 @@
         <v>368</v>
       </c>
       <c r="B25">
-        <v>1.043756996504686</v>
+        <v>1.044321705097611</v>
       </c>
       <c r="C25">
-        <v>0.009560006837673319</v>
+        <v>0.008588552085444607</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1078,10 +1078,10 @@
         <v>375</v>
       </c>
       <c r="B26">
-        <v>1.035966509774393</v>
+        <v>1.036460495998121</v>
       </c>
       <c r="C26">
-        <v>0.02144942249145445</v>
+        <v>0.02064084346755041</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1089,10 +1089,10 @@
         <v>381</v>
       </c>
       <c r="B27">
-        <v>0.9667019832617086</v>
+        <v>0.9670808176329669</v>
       </c>
       <c r="C27">
-        <v>0.01055660303308877</v>
+        <v>0.01008194822810547</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1100,10 +1100,10 @@
         <v>386</v>
       </c>
       <c r="B28">
-        <v>0.9918848521193503</v>
+        <v>0.9922686177770572</v>
       </c>
       <c r="C28">
-        <v>0.04271363842255484</v>
+        <v>0.04205048815697508</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1111,10 +1111,10 @@
         <v>391</v>
       </c>
       <c r="B29">
-        <v>1.045093396613222</v>
+        <v>1.045863855882893</v>
       </c>
       <c r="C29">
-        <v>0.02749813022992709</v>
+        <v>0.02627492716835366</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1122,10 +1122,10 @@
         <v>396</v>
       </c>
       <c r="B30">
-        <v>1.009050090344697</v>
+        <v>1.009471566287224</v>
       </c>
       <c r="C30">
-        <v>0.01167331759604665</v>
+        <v>0.01220599843296431</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1133,10 +1133,10 @@
         <v>398</v>
       </c>
       <c r="B31">
-        <v>1.017016423166986</v>
+        <v>1.017316712268334</v>
       </c>
       <c r="C31">
-        <v>0.01317056700031759</v>
+        <v>0.01347000999772967</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1144,10 +1144,10 @@
         <v>418</v>
       </c>
       <c r="B32">
-        <v>1.052772004302769</v>
+        <v>1.052990866009557</v>
       </c>
       <c r="C32">
-        <v>0.02394049764134658</v>
+        <v>0.02372648590119197</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1155,10 +1155,10 @@
         <v>419</v>
       </c>
       <c r="B33">
-        <v>1.04857276220095</v>
+        <v>1.048762590424782</v>
       </c>
       <c r="C33">
-        <v>0.02852957327387932</v>
+        <v>0.02837314189205063</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1166,10 +1166,10 @@
         <v>423</v>
       </c>
       <c r="B34">
-        <v>1.048557661834762</v>
+        <v>1.049027176148103</v>
       </c>
       <c r="C34">
-        <v>0.01947054830640468</v>
+        <v>0.01868123990900961</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1177,10 +1177,10 @@
         <v>424</v>
       </c>
       <c r="B35">
-        <v>1.041231449207298</v>
+        <v>1.041742472345472</v>
       </c>
       <c r="C35">
-        <v>0.02157001958979718</v>
+        <v>0.02082634774837571</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1188,10 +1188,10 @@
         <v>428</v>
       </c>
       <c r="B36">
-        <v>1.00334404563618</v>
+        <v>1.004140572816641</v>
       </c>
       <c r="C36">
-        <v>0.02067242179141131</v>
+        <v>0.02181079911771549</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1199,10 +1199,10 @@
         <v>447</v>
       </c>
       <c r="B37">
-        <v>0.9759802767175737</v>
+        <v>0.9761206349311635</v>
       </c>
       <c r="C37">
-        <v>0.01939891140411872</v>
+        <v>0.01932631583328269</v>
       </c>
     </row>
   </sheetData>
@@ -1228,10 +1228,10 @@
         <v>24</v>
       </c>
       <c r="B2">
-        <v>1.316418486097396</v>
+        <v>1.316970780662437</v>
       </c>
       <c r="C2">
-        <v>0.05185662755739281</v>
+        <v>0.05133319035583303</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1239,10 +1239,10 @@
         <v>26</v>
       </c>
       <c r="B3">
-        <v>1.348619977247455</v>
+        <v>1.349161858900877</v>
       </c>
       <c r="C3">
-        <v>0.0249634074265094</v>
+        <v>0.02440903922756779</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1250,10 +1250,10 @@
         <v>31</v>
       </c>
       <c r="B4">
-        <v>1.433698433921209</v>
+        <v>1.433895304410263</v>
       </c>
       <c r="C4">
-        <v>0.02825983893633686</v>
+        <v>0.02853955486020558</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1261,10 +1261,10 @@
         <v>32</v>
       </c>
       <c r="B5">
-        <v>1.461304070947413</v>
+        <v>1.461533127002298</v>
       </c>
       <c r="C5">
-        <v>0.02021805086694393</v>
+        <v>0.02052126107353085</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1272,10 +1272,10 @@
         <v>33</v>
       </c>
       <c r="B6">
-        <v>1.410799060444235</v>
+        <v>1.411104149723005</v>
       </c>
       <c r="C6">
-        <v>0.01894233545911306</v>
+        <v>0.01913058262993437</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1283,10 +1283,10 @@
         <v>67</v>
       </c>
       <c r="B7">
-        <v>1.201773356840331</v>
+        <v>1.202468395863371</v>
       </c>
       <c r="C7">
-        <v>0.01456697204673263</v>
+        <v>0.01336459572959412</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1294,10 +1294,10 @@
         <v>190</v>
       </c>
       <c r="B8">
-        <v>1.192206358491634</v>
+        <v>1.192968005938493</v>
       </c>
       <c r="C8">
-        <v>0.0275925244468603</v>
+        <v>0.02690508378695721</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1305,10 +1305,10 @@
         <v>211</v>
       </c>
       <c r="B9">
-        <v>1.343138025131222</v>
+        <v>1.343655359192825</v>
       </c>
       <c r="C9">
-        <v>0.01071991002042437</v>
+        <v>0.01138066913051992</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1316,10 +1316,10 @@
         <v>212</v>
       </c>
       <c r="B10">
-        <v>1.342163426443299</v>
+        <v>1.342887990647278</v>
       </c>
       <c r="C10">
-        <v>0.007797996767972521</v>
+        <v>0.008810489967882786</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1327,10 +1327,10 @@
         <v>231</v>
       </c>
       <c r="B11">
-        <v>1.591025576319808</v>
+        <v>1.591920306428828</v>
       </c>
       <c r="C11">
-        <v>0.05248746228112499</v>
+        <v>0.05114462322806114</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1338,10 +1338,10 @@
         <v>232</v>
       </c>
       <c r="B12">
-        <v>1.675791318369606</v>
+        <v>1.676546088017762</v>
       </c>
       <c r="C12">
-        <v>0.07164977994685014</v>
+        <v>0.07076969391236</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1349,10 +1349,10 @@
         <v>234</v>
       </c>
       <c r="B13">
-        <v>1.758148187453348</v>
+        <v>1.75876484245392</v>
       </c>
       <c r="C13">
-        <v>0.0465810915976784</v>
+        <v>0.04608541699022967</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1360,10 +1360,10 @@
         <v>235</v>
       </c>
       <c r="B14">
-        <v>1.774312104696199</v>
+        <v>1.774905706019644</v>
       </c>
       <c r="C14">
-        <v>0.02524281453779177</v>
+        <v>0.02454756042133978</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1371,10 +1371,10 @@
         <v>237</v>
       </c>
       <c r="B15">
-        <v>1.730850858004133</v>
+        <v>1.7314749117057</v>
       </c>
       <c r="C15">
-        <v>0.02342032442532474</v>
+        <v>0.0238656147471001</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1382,10 +1382,10 @@
         <v>240</v>
       </c>
       <c r="B16">
-        <v>1.732388371023021</v>
+        <v>1.732927187703152</v>
       </c>
       <c r="C16">
-        <v>0.01882859677676657</v>
+        <v>0.01975383626765677</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1393,10 +1393,10 @@
         <v>241</v>
       </c>
       <c r="B17">
-        <v>1.737529326855556</v>
+        <v>1.737953454799223</v>
       </c>
       <c r="C17">
-        <v>0.007405611811542344</v>
+        <v>0.007624370912262861</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1404,10 +1404,10 @@
         <v>242</v>
       </c>
       <c r="B18">
-        <v>1.687806353847591</v>
+        <v>1.68825987087455</v>
       </c>
       <c r="C18">
-        <v>0.02361315151423415</v>
+        <v>0.02334662743138258</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1415,10 +1415,10 @@
         <v>245</v>
       </c>
       <c r="B19">
-        <v>1.454587162759847</v>
+        <v>1.4550284292683</v>
       </c>
       <c r="C19">
-        <v>0.0007471137088801962</v>
+        <v>0.0007834628058657392</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1426,10 +1426,10 @@
         <v>256</v>
       </c>
       <c r="B20">
-        <v>1.28042961077894</v>
+        <v>1.28119609906813</v>
       </c>
       <c r="C20">
-        <v>0.01445618177451274</v>
+        <v>0.0157668724071131</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1437,10 +1437,10 @@
         <v>262</v>
       </c>
       <c r="B21">
-        <v>1.264463242730103</v>
+        <v>1.265069457390021</v>
       </c>
       <c r="C21">
-        <v>0.01854285185829073</v>
+        <v>0.01833412243014922</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1448,10 +1448,10 @@
         <v>272</v>
       </c>
       <c r="B22">
-        <v>1.197594036802413</v>
+        <v>1.198040213813923</v>
       </c>
       <c r="C22">
-        <v>0.005983237034429318</v>
+        <v>0.006417357829653805</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1459,10 +1459,10 @@
         <v>316</v>
       </c>
       <c r="B23">
-        <v>1.143508286993709</v>
+        <v>1.14393982762003</v>
       </c>
       <c r="C23">
-        <v>0.01711118555513981</v>
+        <v>0.0176879388200428</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1470,10 +1470,10 @@
         <v>341</v>
       </c>
       <c r="B24">
-        <v>1.108222793517999</v>
+        <v>1.10844912193349</v>
       </c>
       <c r="C24">
-        <v>0.03692826037979645</v>
+        <v>0.03675687873594441</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1481,10 +1481,10 @@
         <v>383</v>
       </c>
       <c r="B25">
-        <v>1.124608251625253</v>
+        <v>1.125007533971317</v>
       </c>
       <c r="C25">
-        <v>0.0119495887052747</v>
+        <v>0.01174961434643707</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1492,10 +1492,10 @@
         <v>432</v>
       </c>
       <c r="B26">
-        <v>1.195099188515154</v>
+        <v>1.195695927049739</v>
       </c>
       <c r="C26">
-        <v>0.00333378826119908</v>
+        <v>0.002390562950112386</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1503,10 +1503,10 @@
         <v>439</v>
       </c>
       <c r="B27">
-        <v>1.237966100144601</v>
+        <v>1.238528506684952</v>
       </c>
       <c r="C27">
-        <v>0.06174768786956707</v>
+        <v>0.06142909955959414</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1514,10 +1514,10 @@
         <v>443</v>
       </c>
       <c r="B28">
-        <v>1.213857841666075</v>
+        <v>1.214271176732085</v>
       </c>
       <c r="C28">
-        <v>0.02265498926632926</v>
+        <v>0.02251986471315011</v>
       </c>
     </row>
   </sheetData>
@@ -1543,10 +1543,10 @@
         <v>22</v>
       </c>
       <c r="B2">
-        <v>1.211196155768988</v>
+        <v>1.211594518374651</v>
       </c>
       <c r="C2">
-        <v>0.03310185599514665</v>
+        <v>0.03266538588369509</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1554,10 +1554,10 @@
         <v>133</v>
       </c>
       <c r="B3">
-        <v>1.047645982707711</v>
+        <v>1.047706036660747</v>
       </c>
       <c r="C3">
-        <v>0.01539346649318539</v>
+        <v>0.01549453849452458</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1565,10 +1565,10 @@
         <v>249</v>
       </c>
       <c r="B4">
-        <v>1.248736801356773</v>
+        <v>1.249067944703657</v>
       </c>
       <c r="C4">
-        <v>0.02076741391265715</v>
+        <v>0.02119033123290068</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1576,10 +1576,10 @@
         <v>250</v>
       </c>
       <c r="B5">
-        <v>1.237835306126197</v>
+        <v>1.238258488678364</v>
       </c>
       <c r="C5">
-        <v>0.01083197963246111</v>
+        <v>0.01137015781038798</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1587,10 +1587,10 @@
         <v>263</v>
       </c>
       <c r="B6">
-        <v>1.24249499563638</v>
+        <v>1.242925458974954</v>
       </c>
       <c r="C6">
-        <v>0.008696432868775333</v>
+        <v>0.009169782757140366</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1598,10 +1598,10 @@
         <v>314</v>
       </c>
       <c r="B7">
-        <v>1.097193236998308</v>
+        <v>1.097708899352774</v>
       </c>
       <c r="C7">
-        <v>0.01146748814348189</v>
+        <v>0.01142510357013328</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1609,10 +1609,10 @@
         <v>317</v>
       </c>
       <c r="B8">
-        <v>1.131816145538175</v>
+        <v>1.132165366545494</v>
       </c>
       <c r="C8">
-        <v>0.02021942796611114</v>
+        <v>0.02072150799210656</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1620,10 +1620,10 @@
         <v>318</v>
       </c>
       <c r="B9">
-        <v>1.110188190125642</v>
+        <v>1.110590990266297</v>
       </c>
       <c r="C9">
-        <v>0.01802674230535381</v>
+        <v>0.01860976294851495</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1631,10 +1631,10 @@
         <v>349</v>
       </c>
       <c r="B10">
-        <v>1.0333207160484</v>
+        <v>1.033703811918157</v>
       </c>
       <c r="C10">
-        <v>0.01813903673606845</v>
+        <v>0.01858724230315642</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1642,10 +1642,10 @@
         <v>366</v>
       </c>
       <c r="B11">
-        <v>1.011478029382128</v>
+        <v>1.011881870048034</v>
       </c>
       <c r="C11">
-        <v>0.01350279042669022</v>
+        <v>0.01413220839631308</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1653,10 +1653,10 @@
         <v>376</v>
       </c>
       <c r="B12">
-        <v>1.061916514027423</v>
+        <v>1.062407717620991</v>
       </c>
       <c r="C12">
-        <v>0.02273928406725915</v>
+        <v>0.02189468929626926</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1664,10 +1664,10 @@
         <v>378</v>
       </c>
       <c r="B13">
-        <v>1.045067162953105</v>
+        <v>1.045461985651723</v>
       </c>
       <c r="C13">
-        <v>0.01838843707410252</v>
+        <v>0.01770931907283244</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1675,10 +1675,10 @@
         <v>394</v>
       </c>
       <c r="B14">
-        <v>1.039319748029411</v>
+        <v>1.039684263297878</v>
       </c>
       <c r="C14">
-        <v>0.01308586694767761</v>
+        <v>0.01245597109375238</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1686,10 +1686,10 @@
         <v>403</v>
       </c>
       <c r="B15">
-        <v>1.035010500102874</v>
+        <v>1.0355714997977</v>
       </c>
       <c r="C15">
-        <v>0.004926563325190915</v>
+        <v>0.004455684413796899</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1697,10 +1697,10 @@
         <v>407</v>
       </c>
       <c r="B16">
-        <v>1.04249373654096</v>
+        <v>1.042809395260903</v>
       </c>
       <c r="C16">
-        <v>0.01924834452707647</v>
+        <v>0.01888702885145036</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1708,10 +1708,10 @@
         <v>408</v>
       </c>
       <c r="B17">
-        <v>1.040842545100621</v>
+        <v>1.04119269592807</v>
       </c>
       <c r="C17">
-        <v>0.02109116548248972</v>
+        <v>0.0208122401664133</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1719,10 +1719,10 @@
         <v>409</v>
       </c>
       <c r="B18">
-        <v>1.040924824040337</v>
+        <v>1.041294328297252</v>
       </c>
       <c r="C18">
-        <v>0.01593531794640247</v>
+        <v>0.01561156152710736</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1730,10 +1730,10 @@
         <v>426</v>
       </c>
       <c r="B19">
-        <v>1.087852475346333</v>
+        <v>1.088496788677343</v>
       </c>
       <c r="C19">
-        <v>0.02016558792829822</v>
+        <v>0.02078482823810062</v>
       </c>
     </row>
   </sheetData>
@@ -1759,10 +1759,10 @@
         <v>24</v>
       </c>
       <c r="B2">
-        <v>0.9982642315439181</v>
+        <v>0.9986104470437249</v>
       </c>
       <c r="C2">
-        <v>0.02694401629460798</v>
+        <v>0.02690704349680739</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1770,10 +1770,10 @@
         <v>26</v>
       </c>
       <c r="B3">
-        <v>1.014577319396327</v>
+        <v>1.014910852318703</v>
       </c>
       <c r="C3">
-        <v>0.01085248424729257</v>
+        <v>0.01103726883955974</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1781,10 +1781,10 @@
         <v>31</v>
       </c>
       <c r="B4">
-        <v>1.024179490448327</v>
+        <v>1.024513903732348</v>
       </c>
       <c r="C4">
-        <v>0.01770076709024757</v>
+        <v>0.01787477576567811</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1792,10 +1792,10 @@
         <v>32</v>
       </c>
       <c r="B5">
-        <v>1.030553665917469</v>
+        <v>1.030972327195548</v>
       </c>
       <c r="C5">
-        <v>0.0137245882885516</v>
+        <v>0.01352332340451648</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1803,10 +1803,10 @@
         <v>33</v>
       </c>
       <c r="B6">
-        <v>1.023801372077795</v>
+        <v>1.024180690512903</v>
       </c>
       <c r="C6">
-        <v>0.01322948267820529</v>
+        <v>0.01276088538999048</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1814,10 +1814,10 @@
         <v>67</v>
       </c>
       <c r="B7">
-        <v>1.106998379123648</v>
+        <v>1.107588871830471</v>
       </c>
       <c r="C7">
-        <v>0.01077316313619616</v>
+        <v>0.01146319034551917</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1825,10 +1825,10 @@
         <v>190</v>
       </c>
       <c r="B8">
-        <v>1.060371256915958</v>
+        <v>1.060975726340446</v>
       </c>
       <c r="C8">
-        <v>0.02077563465171296</v>
+        <v>0.02064355167498296</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1836,10 +1836,10 @@
         <v>211</v>
       </c>
       <c r="B9">
-        <v>0.9980671517965307</v>
+        <v>0.998251644193601</v>
       </c>
       <c r="C9">
-        <v>0.01857348966695744</v>
+        <v>0.01832915681966492</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1847,10 +1847,10 @@
         <v>212</v>
       </c>
       <c r="B10">
-        <v>0.9954359671812965</v>
+        <v>0.9956112274454588</v>
       </c>
       <c r="C10">
-        <v>0.01301634957769775</v>
+        <v>0.0128321505164075</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1858,10 +1858,10 @@
         <v>231</v>
       </c>
       <c r="B11">
-        <v>0.995776439476208</v>
+        <v>0.9965446613410097</v>
       </c>
       <c r="C11">
-        <v>0.02290282551361236</v>
+        <v>0.02157508618436247</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1869,10 +1869,10 @@
         <v>232</v>
       </c>
       <c r="B12">
-        <v>0.9854273073820757</v>
+        <v>0.9860950686869513</v>
       </c>
       <c r="C12">
-        <v>0.01452518293236724</v>
+        <v>0.01379141398951302</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1880,10 +1880,10 @@
         <v>234</v>
       </c>
       <c r="B13">
-        <v>0.9971225087058232</v>
+        <v>0.9976766427699478</v>
       </c>
       <c r="C13">
-        <v>0.03450104691777886</v>
+        <v>0.03510549575408906</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1891,10 +1891,10 @@
         <v>235</v>
       </c>
       <c r="B14">
-        <v>0.9970106380222957</v>
+        <v>0.9974892203930236</v>
       </c>
       <c r="C14">
-        <v>0.03748316122173165</v>
+        <v>0.03796273738749817</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1902,10 +1902,10 @@
         <v>237</v>
       </c>
       <c r="B15">
-        <v>0.9818544540336352</v>
+        <v>0.9822137896314643</v>
       </c>
       <c r="C15">
-        <v>0.01664247346082166</v>
+        <v>0.01684791200768486</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1913,10 +1913,10 @@
         <v>240</v>
       </c>
       <c r="B16">
-        <v>0.9709728232347145</v>
+        <v>0.971240588485332</v>
       </c>
       <c r="C16">
-        <v>0.008319025618721831</v>
+        <v>0.008644184203121082</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1924,10 +1924,10 @@
         <v>241</v>
       </c>
       <c r="B17">
-        <v>0.9730883285413011</v>
+        <v>0.9733868233407964</v>
       </c>
       <c r="C17">
-        <v>0.01149374100392304</v>
+        <v>0.01115376051262186</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1935,10 +1935,10 @@
         <v>242</v>
       </c>
       <c r="B18">
-        <v>0.9693851825268768</v>
+        <v>0.9697570134288144</v>
       </c>
       <c r="C18">
-        <v>0.01673334018444445</v>
+        <v>0.01615967511480392</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1946,10 +1946,10 @@
         <v>245</v>
       </c>
       <c r="B19">
-        <v>0.9561577022089524</v>
+        <v>0.9564975602991246</v>
       </c>
       <c r="C19">
-        <v>0.009500843538357492</v>
+        <v>0.009855881848104967</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1957,10 +1957,10 @@
         <v>256</v>
       </c>
       <c r="B20">
-        <v>0.9699645900441588</v>
+        <v>0.9705339622108985</v>
       </c>
       <c r="C20">
-        <v>0.02561448819029593</v>
+        <v>0.02632355259026629</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1968,10 +1968,10 @@
         <v>262</v>
       </c>
       <c r="B21">
-        <v>0.972050477504856</v>
+        <v>0.9725526518511041</v>
       </c>
       <c r="C21">
-        <v>0.005306576757387242</v>
+        <v>0.005254587717026126</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1979,10 +1979,10 @@
         <v>272</v>
       </c>
       <c r="B22">
-        <v>0.9947336252403493</v>
+        <v>0.9950579946219231</v>
       </c>
       <c r="C22">
-        <v>0.01313229391757921</v>
+        <v>0.01275481258560799</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1990,10 +1990,10 @@
         <v>316</v>
       </c>
       <c r="B23">
-        <v>0.9562731249481135</v>
+        <v>0.9564995044066448</v>
       </c>
       <c r="C23">
-        <v>0.02426212959557433</v>
+        <v>0.02399689080155907</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -2001,10 +2001,10 @@
         <v>341</v>
       </c>
       <c r="B24">
-        <v>0.9742451497090704</v>
+        <v>0.974732432902532</v>
       </c>
       <c r="C24">
-        <v>0.01793303333008031</v>
+        <v>0.01748683821261933</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2012,10 +2012,10 @@
         <v>383</v>
       </c>
       <c r="B25">
-        <v>1.022986713771426</v>
+        <v>1.023263479919519</v>
       </c>
       <c r="C25">
-        <v>0.01798325165441144</v>
+        <v>0.01751589503573852</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -2023,10 +2023,10 @@
         <v>432</v>
       </c>
       <c r="B26">
-        <v>1.033538584232792</v>
+        <v>1.033886222137665</v>
       </c>
       <c r="C26">
-        <v>0.01547553380162255</v>
+        <v>0.01542137063859362</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2034,10 +2034,10 @@
         <v>439</v>
       </c>
       <c r="B27">
-        <v>1.034954586464862</v>
+        <v>1.035126775701173</v>
       </c>
       <c r="C27">
-        <v>0.008015497116211969</v>
+        <v>0.008265704364500026</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -2045,10 +2045,10 @@
         <v>443</v>
       </c>
       <c r="B28">
-        <v>1.047803780607539</v>
+        <v>1.047977604789702</v>
       </c>
       <c r="C28">
-        <v>0.02013931713022707</v>
+        <v>0.01986075778571851</v>
       </c>
     </row>
   </sheetData>
@@ -2074,10 +2074,10 @@
         <v>24</v>
       </c>
       <c r="B2">
-        <v>0.8814248778122704</v>
+        <v>0.8818096017695299</v>
       </c>
       <c r="C2">
-        <v>0.04093385065946266</v>
+        <v>0.04066382505215737</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2085,10 +2085,10 @@
         <v>26</v>
       </c>
       <c r="B3">
-        <v>0.8621582911559861</v>
+        <v>0.8627095923511457</v>
       </c>
       <c r="C3">
-        <v>0.0230874457595562</v>
+        <v>0.02222468338361352</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2096,10 +2096,10 @@
         <v>31</v>
       </c>
       <c r="B4">
-        <v>0.8075925852684162</v>
+        <v>0.807951136800697</v>
       </c>
       <c r="C4">
-        <v>0.01278344267998838</v>
+        <v>0.01222058246175406</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2107,10 +2107,10 @@
         <v>32</v>
       </c>
       <c r="B5">
-        <v>0.7970653710247708</v>
+        <v>0.797403493526342</v>
       </c>
       <c r="C5">
-        <v>0.006473082713152827</v>
+        <v>0.005989574457216102</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2118,10 +2118,10 @@
         <v>33</v>
       </c>
       <c r="B6">
-        <v>0.8074516289011552</v>
+        <v>0.8077974941238475</v>
       </c>
       <c r="C6">
-        <v>0.02120033580316436</v>
+        <v>0.02101594892367532</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2129,10 +2129,10 @@
         <v>67</v>
       </c>
       <c r="B7">
-        <v>1.019200659702172</v>
+        <v>1.020069341843112</v>
       </c>
       <c r="C7">
-        <v>0.01250456205498282</v>
+        <v>0.01322228215829952</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2140,10 +2140,10 @@
         <v>190</v>
       </c>
       <c r="B8">
-        <v>0.9582947764248863</v>
+        <v>0.9588915876007643</v>
       </c>
       <c r="C8">
-        <v>0.02021623434968871</v>
+        <v>0.02026369968242731</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2151,10 +2151,10 @@
         <v>211</v>
       </c>
       <c r="B9">
-        <v>0.8450260365273051</v>
+        <v>0.845211467395054</v>
       </c>
       <c r="C9">
-        <v>0.03869641023671186</v>
+        <v>0.03867604302457029</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2162,10 +2162,10 @@
         <v>212</v>
       </c>
       <c r="B10">
-        <v>0.8532045145352315</v>
+        <v>0.8533884129489145</v>
       </c>
       <c r="C10">
-        <v>0.0347274836715246</v>
+        <v>0.03477359569783471</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2173,10 +2173,10 @@
         <v>231</v>
       </c>
       <c r="B11">
-        <v>0.7964912043029538</v>
+        <v>0.7967341231118786</v>
       </c>
       <c r="C11">
-        <v>0.02819671258902452</v>
+        <v>0.02789272421233813</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2184,10 +2184,10 @@
         <v>232</v>
       </c>
       <c r="B12">
-        <v>0.784856201243516</v>
+        <v>0.7851198587585154</v>
       </c>
       <c r="C12">
-        <v>0.02579895020395221</v>
+        <v>0.02544421296955652</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2195,10 +2195,10 @@
         <v>234</v>
       </c>
       <c r="B13">
-        <v>0.7657018292524828</v>
+        <v>0.7658971047911954</v>
       </c>
       <c r="C13">
-        <v>0.02445198994888006</v>
+        <v>0.02435858662694726</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2206,10 +2206,10 @@
         <v>235</v>
       </c>
       <c r="B14">
-        <v>0.7563161222697516</v>
+        <v>0.756578488592664</v>
       </c>
       <c r="C14">
-        <v>0.02605903874260852</v>
+        <v>0.02588120067927727</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2217,10 +2217,10 @@
         <v>237</v>
       </c>
       <c r="B15">
-        <v>0.7512512037589776</v>
+        <v>0.75153665302436</v>
       </c>
       <c r="C15">
-        <v>0.01759453462383244</v>
+        <v>0.01774938556623379</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -2228,10 +2228,10 @@
         <v>240</v>
       </c>
       <c r="B16">
-        <v>0.7392224809057372</v>
+        <v>0.7393647214921256</v>
       </c>
       <c r="C16">
-        <v>0.007578841730619706</v>
+        <v>0.007333907427498615</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2239,10 +2239,10 @@
         <v>241</v>
       </c>
       <c r="B17">
-        <v>0.7416703919937612</v>
+        <v>0.741892077078926</v>
       </c>
       <c r="C17">
-        <v>0.008935224222173898</v>
+        <v>0.008554599859174972</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2250,10 +2250,10 @@
         <v>242</v>
       </c>
       <c r="B18">
-        <v>0.7631294619426413</v>
+        <v>0.7633305629678504</v>
       </c>
       <c r="C18">
-        <v>0.005491617339011043</v>
+        <v>0.005149428762247492</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2261,10 +2261,10 @@
         <v>245</v>
       </c>
       <c r="B19">
-        <v>0.8056603578943288</v>
+        <v>0.8061774777895234</v>
       </c>
       <c r="C19">
-        <v>0.008066832711102862</v>
+        <v>0.008481754948017516</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2272,10 +2272,10 @@
         <v>256</v>
       </c>
       <c r="B20">
-        <v>0.9000863744931671</v>
+        <v>0.9004227623679325</v>
       </c>
       <c r="C20">
-        <v>0.03055691322162069</v>
+        <v>0.03039879682213155</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -2283,10 +2283,10 @@
         <v>262</v>
       </c>
       <c r="B21">
-        <v>0.9059234248151923</v>
+        <v>0.9065911135924395</v>
       </c>
       <c r="C21">
-        <v>0.01982703122570281</v>
+        <v>0.02088481351649787</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -2294,10 +2294,10 @@
         <v>272</v>
       </c>
       <c r="B22">
-        <v>0.9135722886092502</v>
+        <v>0.9140285060530182</v>
       </c>
       <c r="C22">
-        <v>0.02598056477387605</v>
+        <v>0.02677022242015211</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2305,10 +2305,10 @@
         <v>316</v>
       </c>
       <c r="B23">
-        <v>0.9141668304703855</v>
+        <v>0.9148239659790441</v>
       </c>
       <c r="C23">
-        <v>0.0303391683333032</v>
+        <v>0.03034388170069633</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -2316,10 +2316,10 @@
         <v>341</v>
       </c>
       <c r="B24">
-        <v>0.895501593887906</v>
+        <v>0.8958793900251201</v>
       </c>
       <c r="C24">
-        <v>0.01800772588818901</v>
+        <v>0.01735961305712178</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2327,10 +2327,10 @@
         <v>383</v>
       </c>
       <c r="B25">
-        <v>0.934594419051245</v>
+        <v>0.9349452566254127</v>
       </c>
       <c r="C25">
-        <v>0.02459944746907874</v>
+        <v>0.02400326646945818</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -2338,10 +2338,10 @@
         <v>432</v>
       </c>
       <c r="B26">
-        <v>0.934189810109806</v>
+        <v>0.9348594806329807</v>
       </c>
       <c r="C26">
-        <v>0.03191206476701891</v>
+        <v>0.03261370854957914</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2349,10 +2349,10 @@
         <v>439</v>
       </c>
       <c r="B27">
-        <v>0.9052607113770016</v>
+        <v>0.9053981586688454</v>
       </c>
       <c r="C27">
-        <v>0.005141036508851241</v>
+        <v>0.005166636955180516</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -2360,10 +2360,10 @@
         <v>443</v>
       </c>
       <c r="B28">
-        <v>0.9168855587752214</v>
+        <v>0.9170743675745574</v>
       </c>
       <c r="C28">
-        <v>0.01335394892427099</v>
+        <v>0.01350779667656728</v>
       </c>
     </row>
   </sheetData>
@@ -2389,10 +2389,10 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>1.0886672323188</v>
+        <v>1.089051450148715</v>
       </c>
       <c r="C2">
-        <v>0.04024933589698557</v>
+        <v>0.04085256258733418</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2400,10 +2400,10 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>1.044092344247093</v>
+        <v>1.044678783538731</v>
       </c>
       <c r="C3">
-        <v>0.02265744993785149</v>
+        <v>0.02364506018436264</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2411,10 +2411,10 @@
         <v>19</v>
       </c>
       <c r="B4">
-        <v>0.8225518339314631</v>
+        <v>0.8227750226589921</v>
       </c>
       <c r="C4">
-        <v>0.007352895907469073</v>
+        <v>0.007109336803096319</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2422,10 +2422,10 @@
         <v>23</v>
       </c>
       <c r="B5">
-        <v>0.7251119639468754</v>
+        <v>0.7254183380456626</v>
       </c>
       <c r="C5">
-        <v>0.005182403947914025</v>
+        <v>0.004784725736092369</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2433,10 +2433,10 @@
         <v>43</v>
       </c>
       <c r="B6">
-        <v>1.024661596554172</v>
+        <v>1.02517479049687</v>
       </c>
       <c r="C6">
-        <v>0.01546414129503744</v>
+        <v>0.01633213143541027</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2444,10 +2444,10 @@
         <v>59</v>
       </c>
       <c r="B7">
-        <v>1.113369084273332</v>
+        <v>1.113715228248159</v>
       </c>
       <c r="C7">
-        <v>0.01330961572610212</v>
+        <v>0.01339557971295079</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2455,10 +2455,10 @@
         <v>61</v>
       </c>
       <c r="B8">
-        <v>1.114067351746999</v>
+        <v>1.114535028598862</v>
       </c>
       <c r="C8">
-        <v>0.01605994262109254</v>
+        <v>0.01636697741336527</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2466,10 +2466,10 @@
         <v>142</v>
       </c>
       <c r="B9">
-        <v>1.472744974060282</v>
+        <v>1.473648581446761</v>
       </c>
       <c r="C9">
-        <v>0.03132963354153229</v>
+        <v>0.03001985838589695</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2477,10 +2477,10 @@
         <v>144</v>
       </c>
       <c r="B10">
-        <v>1.547470168511442</v>
+        <v>1.547990013816987</v>
       </c>
       <c r="C10">
-        <v>0.008221860351196226</v>
+        <v>0.008409368315850076</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2488,10 +2488,10 @@
         <v>167</v>
       </c>
       <c r="B11">
-        <v>1.099587963550181</v>
+        <v>1.099858388891895</v>
       </c>
       <c r="C11">
-        <v>0.03008048261592521</v>
+        <v>0.03028998931166672</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2499,10 +2499,10 @@
         <v>170</v>
       </c>
       <c r="B12">
-        <v>1.104238346337147</v>
+        <v>1.104565898125486</v>
       </c>
       <c r="C12">
-        <v>0.03200552097490549</v>
+        <v>0.03170170390799917</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2510,10 +2510,10 @@
         <v>188</v>
       </c>
       <c r="B13">
-        <v>1.151977881230537</v>
+        <v>1.152384658087992</v>
       </c>
       <c r="C13">
-        <v>0.01714814143353533</v>
+        <v>0.01764555181185843</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2521,10 +2521,10 @@
         <v>189</v>
       </c>
       <c r="B14">
-        <v>1.0762418554813</v>
+        <v>1.076615542862453</v>
       </c>
       <c r="C14">
-        <v>0.02914915658965298</v>
+        <v>0.02976293338129842</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2532,10 +2532,10 @@
         <v>206</v>
       </c>
       <c r="B15">
-        <v>0.953963710663463</v>
+        <v>0.9542809942717226</v>
       </c>
       <c r="C15">
-        <v>0.02775522782243246</v>
+        <v>0.0272604984911586</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -2543,10 +2543,10 @@
         <v>209</v>
       </c>
       <c r="B16">
-        <v>0.8909283271316131</v>
+        <v>0.8911493729788672</v>
       </c>
       <c r="C16">
-        <v>0.02063027828985416</v>
+        <v>0.02027167924522827</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2554,10 +2554,10 @@
         <v>217</v>
       </c>
       <c r="B17">
-        <v>0.8895724584167369</v>
+        <v>0.8898793342512739</v>
       </c>
       <c r="C17">
-        <v>0.01679389666971737</v>
+        <v>0.01679061005991818</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2565,10 +2565,10 @@
         <v>221</v>
       </c>
       <c r="B18">
-        <v>0.8750035847726968</v>
+        <v>0.8751721728174088</v>
       </c>
       <c r="C18">
-        <v>0.01730085087944858</v>
+        <v>0.01714449554072652</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2576,10 +2576,10 @@
         <v>238</v>
       </c>
       <c r="B19">
-        <v>0.655197125680658</v>
+        <v>0.6555584200710055</v>
       </c>
       <c r="C19">
-        <v>0.01867138396155235</v>
+        <v>0.01888097182717928</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2587,10 +2587,10 @@
         <v>260</v>
       </c>
       <c r="B20">
-        <v>0.7528590227986642</v>
+        <v>0.7531629975438213</v>
       </c>
       <c r="C20">
-        <v>0.01760574749091067</v>
+        <v>0.01770730285516842</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -2598,10 +2598,10 @@
         <v>267</v>
       </c>
       <c r="B21">
-        <v>0.8159744308333817</v>
+        <v>0.8162191896217514</v>
       </c>
       <c r="C21">
-        <v>0.01081511292435663</v>
+        <v>0.01119781264806625</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -2609,10 +2609,10 @@
         <v>284</v>
       </c>
       <c r="B22">
-        <v>0.8843387407668021</v>
+        <v>0.8847964288286146</v>
       </c>
       <c r="C22">
-        <v>0.03635814529757012</v>
+        <v>0.03590823773539787</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2620,10 +2620,10 @@
         <v>287</v>
       </c>
       <c r="B23">
-        <v>0.9025857526343666</v>
+        <v>0.9029334772695297</v>
       </c>
       <c r="C23">
-        <v>0.02829865662972487</v>
+        <v>0.02773156296934572</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -2631,10 +2631,10 @@
         <v>298</v>
       </c>
       <c r="B24">
-        <v>0.9372576699383858</v>
+        <v>0.9375567755872668</v>
       </c>
       <c r="C24">
-        <v>0.00974708935666212</v>
+        <v>0.01021545184128114</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2642,10 +2642,10 @@
         <v>305</v>
       </c>
       <c r="B25">
-        <v>0.9106534100254912</v>
+        <v>0.9108672166943403</v>
       </c>
       <c r="C25">
-        <v>0.02283045062542964</v>
+        <v>0.02247235964079951</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -2653,10 +2653,10 @@
         <v>308</v>
       </c>
       <c r="B26">
-        <v>0.9007119518456062</v>
+        <v>0.9010921013729631</v>
       </c>
       <c r="C26">
-        <v>0.03698103946550733</v>
+        <v>0.03638916426976988</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2664,10 +2664,10 @@
         <v>337</v>
       </c>
       <c r="B27">
-        <v>0.7751087942446002</v>
+        <v>0.7753485467574536</v>
       </c>
       <c r="C27">
-        <v>0.006155722807556254</v>
+        <v>0.005772989022852189</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -2675,10 +2675,10 @@
         <v>347</v>
       </c>
       <c r="B28">
-        <v>0.768920237618119</v>
+        <v>0.7691638833814703</v>
       </c>
       <c r="C28">
-        <v>0.0009153342440755826</v>
+        <v>0.001135005483640856</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -2686,10 +2686,10 @@
         <v>354</v>
       </c>
       <c r="B29">
-        <v>0.8960864785212385</v>
+        <v>0.8962113533066381</v>
       </c>
       <c r="C29">
-        <v>0.001337292737225926</v>
+        <v>0.001552043575922222</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -2697,10 +2697,10 @@
         <v>359</v>
       </c>
       <c r="B30">
-        <v>1.059430257043697</v>
+        <v>1.059707524426716</v>
       </c>
       <c r="C30">
-        <v>0.02012557413142365</v>
+        <v>0.0197339409438252</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -2708,10 +2708,10 @@
         <v>371</v>
       </c>
       <c r="B31">
-        <v>1.11550131555752</v>
+        <v>1.116038346069785</v>
       </c>
       <c r="C31">
-        <v>0.008943077871764378</v>
+        <v>0.008211380027574183</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -2719,10 +2719,10 @@
         <v>373</v>
       </c>
       <c r="B32">
-        <v>1.088634130916433</v>
+        <v>1.088956637206608</v>
       </c>
       <c r="C32">
-        <v>0.02143669454815665</v>
+        <v>0.02110648174251938</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -2730,10 +2730,10 @@
         <v>380</v>
       </c>
       <c r="B33">
-        <v>1.077934574500483</v>
+        <v>1.078223505239852</v>
       </c>
       <c r="C33">
-        <v>0.03180127945201272</v>
+        <v>0.03167873773804026</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -2741,10 +2741,10 @@
         <v>405</v>
       </c>
       <c r="B34">
-        <v>0.8104453688229619</v>
+        <v>0.8106970922978299</v>
       </c>
       <c r="C34">
-        <v>0.01930830990868509</v>
+        <v>0.01962386776719824</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -2752,10 +2752,10 @@
         <v>415</v>
       </c>
       <c r="B35">
-        <v>1.138861157688254</v>
+        <v>1.139107889944326</v>
       </c>
       <c r="C35">
-        <v>0.02975732052760953</v>
+        <v>0.0293595707517605</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -2763,10 +2763,10 @@
         <v>421</v>
       </c>
       <c r="B36">
-        <v>1.508835972476025</v>
+        <v>1.509262844129406</v>
       </c>
       <c r="C36">
-        <v>0.02031749069301159</v>
+        <v>0.02024592777118637</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -2774,10 +2774,10 @@
         <v>441</v>
       </c>
       <c r="B37">
-        <v>1.043461950358455</v>
+        <v>1.043999413318831</v>
       </c>
       <c r="C37">
-        <v>0.03699162578507934</v>
+        <v>0.03625835126202831</v>
       </c>
     </row>
   </sheetData>
@@ -2803,10 +2803,10 @@
         <v>22</v>
       </c>
       <c r="B2">
-        <v>0.7258459207085984</v>
+        <v>0.7261656183822113</v>
       </c>
       <c r="C2">
-        <v>0.002960518724679304</v>
+        <v>0.002513663738239398</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2814,10 +2814,10 @@
         <v>133</v>
       </c>
       <c r="B3">
-        <v>1.140143948284988</v>
+        <v>1.140575346572253</v>
       </c>
       <c r="C3">
-        <v>0.02143071955347414</v>
+        <v>0.02179688377982084</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2825,10 +2825,10 @@
         <v>249</v>
       </c>
       <c r="B4">
-        <v>0.6465849519395074</v>
+        <v>0.6469739720409836</v>
       </c>
       <c r="C4">
-        <v>0.005659405897835025</v>
+        <v>0.005611533766930624</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2836,10 +2836,10 @@
         <v>250</v>
       </c>
       <c r="B5">
-        <v>0.6600577274245402</v>
+        <v>0.6605348908424998</v>
       </c>
       <c r="C5">
-        <v>0.01207230252259463</v>
+        <v>0.01252419711277872</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2847,10 +2847,10 @@
         <v>263</v>
       </c>
       <c r="B6">
-        <v>0.7075269784786439</v>
+        <v>0.7079912676282483</v>
       </c>
       <c r="C6">
-        <v>0.007707779072271897</v>
+        <v>0.007513683816552992</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2858,10 +2858,10 @@
         <v>314</v>
       </c>
       <c r="B7">
-        <v>0.7793250240008391</v>
+        <v>0.7795684287711571</v>
       </c>
       <c r="C7">
-        <v>0.02600282488774012</v>
+        <v>0.02558246622770426</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2869,10 +2869,10 @@
         <v>317</v>
       </c>
       <c r="B8">
-        <v>0.6922747836879656</v>
+        <v>0.692384329785115</v>
       </c>
       <c r="C8">
-        <v>0.008683012964935314</v>
+        <v>0.008521278653111199</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2880,10 +2880,10 @@
         <v>318</v>
       </c>
       <c r="B9">
-        <v>0.6991256454537345</v>
+        <v>0.6992209325826556</v>
       </c>
       <c r="C9">
-        <v>0.009388828902666783</v>
+        <v>0.009253788717961836</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2891,10 +2891,10 @@
         <v>349</v>
       </c>
       <c r="B10">
-        <v>0.7953739624091055</v>
+        <v>0.7955196755941983</v>
       </c>
       <c r="C10">
-        <v>0.009839576726070162</v>
+        <v>0.009607097417517547</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2902,10 +2902,10 @@
         <v>366</v>
       </c>
       <c r="B11">
-        <v>1.054170816297379</v>
+        <v>1.054689087907309</v>
       </c>
       <c r="C11">
-        <v>0.009156554297529131</v>
+        <v>0.009785563351909297</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2913,10 +2913,10 @@
         <v>376</v>
       </c>
       <c r="B12">
-        <v>0.9905451479788482</v>
+        <v>0.9907691882602045</v>
       </c>
       <c r="C12">
-        <v>0.02547573773820358</v>
+        <v>0.02573539431880178</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2924,10 +2924,10 @@
         <v>378</v>
       </c>
       <c r="B13">
-        <v>0.9583578435403138</v>
+        <v>0.9586661887396223</v>
       </c>
       <c r="C13">
-        <v>0.01888075045749508</v>
+        <v>0.01886193756495774</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2935,10 +2935,10 @@
         <v>394</v>
       </c>
       <c r="B14">
-        <v>1.13377622191194</v>
+        <v>1.134121567212703</v>
       </c>
       <c r="C14">
-        <v>0.03721837298437966</v>
+        <v>0.03723437948576791</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2946,10 +2946,10 @@
         <v>403</v>
       </c>
       <c r="B15">
-        <v>0.8177808633268295</v>
+        <v>0.8180163802681277</v>
       </c>
       <c r="C15">
-        <v>0.01968923677466403</v>
+        <v>0.01983939994607862</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -2957,10 +2957,10 @@
         <v>407</v>
       </c>
       <c r="B16">
-        <v>0.763200595349696</v>
+        <v>0.763527984349006</v>
       </c>
       <c r="C16">
-        <v>0.01792996611764462</v>
+        <v>0.01788517341552403</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2968,10 +2968,10 @@
         <v>408</v>
       </c>
       <c r="B17">
-        <v>0.7600519452121457</v>
+        <v>0.7603140191552149</v>
       </c>
       <c r="C17">
-        <v>0.01162888796657066</v>
+        <v>0.01169106431733741</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2979,10 +2979,10 @@
         <v>409</v>
       </c>
       <c r="B18">
-        <v>0.7940462092404429</v>
+        <v>0.7942366837566711</v>
       </c>
       <c r="C18">
-        <v>0.003890642343485521</v>
+        <v>0.003561360518968744</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2990,10 +2990,10 @@
         <v>426</v>
       </c>
       <c r="B19">
-        <v>1.256574606320717</v>
+        <v>1.257067535914905</v>
       </c>
       <c r="C19">
-        <v>0.001255329447640494</v>
+        <v>0.002030173871340504</v>
       </c>
     </row>
   </sheetData>
